--- a/results/Int All Data 0.2/Linea_fi_all.xlsx
+++ b/results/Int All Data 0.2/Linea_fi_all.xlsx
@@ -1461,7 +1461,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.06796482412060299 +/- 0.002331935643605674</t>
+          <t>0.06800670016750418 +/- 0.002362937350027794</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.00452261306532663 +/- 0.0028078818449313527</t>
+          <t>0.004564489112227799 +/- 0.0027232312375023667</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.041247906197654914 +/- 0.0022336072618248768</t>
+          <t>0.04120603015075375 +/- 0.0022332146777174727</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>8.375209380231396e-05 +/- 0.0003133716404333308</t>
+          <t>0.00016750418760466123 +/- 0.00027777427054902237</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.007995028997514553 +/- 0.0015725147386994502</t>
+          <t>0.008036454018227068 +/- 0.001627745045931121</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.029168278529980683 +/- 0.0025260855268571946</t>
+          <t>0.02920696324951646 +/- 0.002478540577120546</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.0076208897485493645 +/- 0.002719235863952028</t>
+          <t>0.007582205029013589 +/- 0.0026700864876963207</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>-0.0119922630560928 +/- 0.0012233182437788729</t>
+          <t>-0.012030947775628575 +/- 0.001288265052638033</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-0.004609785685402401 +/- 0.0012554933033772614</t>
+          <t>-0.004650222401941018 +/- 0.0012298347210469363</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>-0.012899312575818889 +/- 0.0010141476913857355</t>
+          <t>-0.013020622725434739 +/- 0.001082012790963188</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.010028305701577034 +/- 0.001542966763310873</t>
+          <t>-0.009947432268499801 +/- 0.0015471998762401154</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>0.009156337465013964 +/- 0.0023069766872053812</t>
+          <t>0.009116353458616522 +/- 0.002357361531064962</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.0005446166736489677 +/- 0.00046082949308756167</t>
+          <t>0.0005865102639296627 +/- 0.0004272324686713664</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>0.04407205697528284 +/- 0.002984752933482529</t>
+          <t>0.04411395056556352 +/- 0.0029328505443129075</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-0.0019142738243861923 +/- 0.0005644885545672324</t>
+          <t>-0.0018726591760299782 +/- 0.0006513722780898151</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-0.00258010819808574 +/- 0.0033695018693295224</t>
+          <t>-0.002621722846441954 +/- 0.0032875572201414953</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.019167962674961125 +/- 0.0029968072585603587</t>
+          <t>0.01912908242612753 +/- 0.0030106470735001426</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.0001166407465007957 +/- 0.0005779964520730467</t>
+          <t>7.776049766720084e-05 +/- 0.0005443234836703028</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.0019185591229443633 +/- 0.0013039017858533016</t>
+          <t>0.001840250587313985 +/- 0.0013109372782132448</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="DX11" t="inlineStr">
         <is>
-          <t>0.017541111981205892 +/- 0.002301791457587938</t>
+          <t>0.017501957713390703 +/- 0.002235910968718745</t>
         </is>
       </c>
       <c r="DY11" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="ET11" t="inlineStr">
         <is>
-          <t>0.02646828504306964 +/- 0.0031284235482283668</t>
+          <t>0.02650743931088484 +/- 0.003161813192360597</t>
         </is>
       </c>
       <c r="EU11" t="inlineStr">
